--- a/mecatronica/lp/frequencia.xlsx
+++ b/mecatronica/lp/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\mecatronica\lp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D214A337-974B-445F-8E5C-2C03186BAE91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EC6A01-76F7-43EE-A208-41D668FD7927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61FC206C-72CD-4264-B2AB-BE85D1DED9B7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="22">
   <si>
     <t>Guilherme Assis Pereira</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -503,16 +506,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C792F40-3E98-4415-93FE-BF383DE9D8A9}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="33" width="6" customWidth="1"/>
+    <col min="6" max="6" width="6" customWidth="1"/>
+    <col min="7" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="33" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B1" s="2">
         <v>45680</v>
       </c>
@@ -528,8 +533,14 @@
       <c r="F1" s="4">
         <v>45708</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="4">
+        <v>45715</v>
+      </c>
+      <c r="H1" s="4">
+        <v>45722</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -548,8 +559,14 @@
       <c r="F2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -568,8 +585,14 @@
       <c r="F3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -588,8 +611,14 @@
       <c r="F4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -608,8 +637,14 @@
       <c r="F5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -628,8 +663,14 @@
       <c r="F6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -648,8 +689,14 @@
       <c r="F7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,8 +715,14 @@
       <c r="F8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -688,8 +741,14 @@
       <c r="F9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -708,8 +767,14 @@
       <c r="F10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -728,8 +793,14 @@
       <c r="F11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -748,8 +819,14 @@
       <c r="F12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -768,8 +845,14 @@
       <c r="F13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -788,8 +871,14 @@
       <c r="F14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -808,8 +897,14 @@
       <c r="F15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -828,8 +923,14 @@
       <c r="F16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -848,8 +949,14 @@
       <c r="F17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -868,8 +975,14 @@
       <c r="F18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,8 +1001,14 @@
       <c r="F19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,6 +1025,12 @@
         <v>20</v>
       </c>
       <c r="F20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" t="s">
         <v>20</v>
       </c>
     </row>

--- a/mecatronica/lp/frequencia.xlsx
+++ b/mecatronica/lp/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\mecatronica\lp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EC6A01-76F7-43EE-A208-41D668FD7927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5361F304-FA3B-4E1D-824A-C4A065F941B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61FC206C-72CD-4264-B2AB-BE85D1DED9B7}"/>
   </bookViews>

--- a/mecatronica/lp/frequencia.xlsx
+++ b/mecatronica/lp/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\mecatronica\lp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5361F304-FA3B-4E1D-824A-C4A065F941B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A10856-4101-47EE-AB0A-FCD23B1C4125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61FC206C-72CD-4264-B2AB-BE85D1DED9B7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="22">
   <si>
     <t>Guilherme Assis Pereira</t>
   </si>
@@ -506,18 +506,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C792F40-3E98-4415-93FE-BF383DE9D8A9}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="33" width="6" customWidth="1"/>
+    <col min="7" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="33" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B1" s="2">
         <v>45680</v>
       </c>
@@ -539,8 +539,11 @@
       <c r="H1" s="4">
         <v>45722</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="4">
+        <v>45729</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -565,8 +568,11 @@
       <c r="H2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -591,8 +597,11 @@
       <c r="H3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -617,8 +626,11 @@
       <c r="H4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -643,8 +655,11 @@
       <c r="H5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -669,8 +684,11 @@
       <c r="H6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -695,8 +713,11 @@
       <c r="H7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -721,8 +742,11 @@
       <c r="H8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -747,8 +771,11 @@
       <c r="H9" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -773,8 +800,11 @@
       <c r="H10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -799,8 +829,11 @@
       <c r="H11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -825,8 +858,11 @@
       <c r="H12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -851,8 +887,11 @@
       <c r="H13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -877,8 +916,11 @@
       <c r="H14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -903,8 +945,11 @@
       <c r="H15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -929,8 +974,11 @@
       <c r="H16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -955,8 +1003,11 @@
       <c r="H17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -981,8 +1032,11 @@
       <c r="H18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -1007,8 +1061,11 @@
       <c r="H19" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
@@ -1031,6 +1088,9 @@
         <v>20</v>
       </c>
       <c r="H20" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" t="s">
         <v>20</v>
       </c>
     </row>

--- a/mecatronica/lp/frequencia.xlsx
+++ b/mecatronica/lp/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Instrutor\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\mecatronica\lp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A10856-4101-47EE-AB0A-FCD23B1C4125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9104CD4-7536-4633-B81D-B7E7F59798FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61FC206C-72CD-4264-B2AB-BE85D1DED9B7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="22">
   <si>
     <t>Guilherme Assis Pereira</t>
   </si>
@@ -506,18 +506,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C792F40-3E98-4415-93FE-BF383DE9D8A9}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" customWidth="1"/>
-    <col min="7" max="9" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="33" width="6" customWidth="1"/>
+    <col min="7" max="10" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="33" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B1" s="2">
         <v>45680</v>
       </c>
@@ -542,8 +542,11 @@
       <c r="I1" s="4">
         <v>45729</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="4">
+        <v>45736</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -571,8 +574,11 @@
       <c r="I2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -600,8 +606,11 @@
       <c r="I3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -629,8 +638,11 @@
       <c r="I4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -658,8 +670,11 @@
       <c r="I5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -687,8 +702,11 @@
       <c r="I6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -716,8 +734,11 @@
       <c r="I7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,8 +766,11 @@
       <c r="I8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -774,8 +798,11 @@
       <c r="I9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>2</v>
       </c>
@@ -803,8 +830,11 @@
       <c r="I10" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,8 +862,11 @@
       <c r="I11" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
@@ -861,8 +894,11 @@
       <c r="I12" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -890,8 +926,11 @@
       <c r="I13" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -919,8 +958,11 @@
       <c r="I14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
@@ -948,8 +990,11 @@
       <c r="I15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -977,8 +1022,11 @@
       <c r="I16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -1006,8 +1054,11 @@
       <c r="I17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -1035,8 +1086,11 @@
       <c r="I18" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>7</v>
       </c>
@@ -1064,8 +1118,11 @@
       <c r="I19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>8</v>
       </c>
@@ -1092,6 +1149,9 @@
       </c>
       <c r="I20" t="s">
         <v>20</v>
+      </c>
+      <c r="J20" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
